--- a/INSTANCES/instances_xlsx/A_MTN_3/231FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/231FL_10A_3.xlsx
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7772,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
